--- a/database/final_coffee_library_v342.xlsx
+++ b/database/final_coffee_library_v342.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WIN 10\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tawlefti\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" firstSheet="1" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20496" windowHeight="7656" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Metrics Key" sheetId="1" r:id="rId1"/>
@@ -9319,9 +9319,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -9349,7 +9349,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -9363,7 +9363,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -9377,7 +9377,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -9405,7 +9405,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -9419,7 +9419,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -9433,7 +9433,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -9447,7 +9447,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -9461,7 +9461,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -9475,7 +9475,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -9489,7 +9489,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -9503,7 +9503,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -9517,7 +9517,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -9531,7 +9531,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -9559,7 +9559,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -9573,7 +9573,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -9587,7 +9587,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -9601,7 +9601,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -9615,7 +9615,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -9637,17 +9637,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L67"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="6" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="34" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" customWidth="1"/>
-    <col min="9" max="10" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="27.5703125" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="50.42578125" customWidth="1"/>
+    <col min="3" max="3" width="41" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="8" width="50.6640625" customWidth="1"/>
+    <col min="9" max="10" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="27.5546875" customWidth="1"/>
+    <col min="12" max="12" width="50.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -9685,7 +9688,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -9723,7 +9726,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -9761,7 +9764,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -9799,7 +9802,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -9837,7 +9840,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>63</v>
       </c>
@@ -9875,7 +9878,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -9913,7 +9916,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -9951,7 +9954,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>63</v>
       </c>
@@ -9989,7 +9992,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>63</v>
       </c>
@@ -10027,7 +10030,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>63</v>
       </c>
@@ -10065,7 +10068,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -10103,7 +10106,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -10141,7 +10144,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>63</v>
       </c>
@@ -10179,7 +10182,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>63</v>
       </c>
@@ -10217,7 +10220,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -10255,7 +10258,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -10293,7 +10296,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -10331,7 +10334,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>63</v>
       </c>
@@ -10369,7 +10372,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -10407,7 +10410,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -10445,7 +10448,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -10483,7 +10486,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>63</v>
       </c>
@@ -10521,7 +10524,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>64</v>
       </c>
@@ -10559,7 +10562,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>64</v>
       </c>
@@ -10597,7 +10600,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -10635,7 +10638,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -10673,7 +10676,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>64</v>
       </c>
@@ -10711,7 +10714,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>64</v>
       </c>
@@ -10749,7 +10752,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -10787,7 +10790,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -10825,7 +10828,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>64</v>
       </c>
@@ -10863,7 +10866,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>64</v>
       </c>
@@ -10901,7 +10904,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -10939,7 +10942,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>64</v>
       </c>
@@ -10977,7 +10980,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>64</v>
       </c>
@@ -11015,7 +11018,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>64</v>
       </c>
@@ -11053,7 +11056,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -11091,7 +11094,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>64</v>
       </c>
@@ -11129,7 +11132,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>64</v>
       </c>
@@ -11167,7 +11170,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>64</v>
       </c>
@@ -11205,7 +11208,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>64</v>
       </c>
@@ -11243,7 +11246,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>64</v>
       </c>
@@ -11281,7 +11284,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>64</v>
       </c>
@@ -11319,7 +11322,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>64</v>
       </c>
@@ -11357,7 +11360,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>62</v>
       </c>
@@ -11395,7 +11398,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>62</v>
       </c>
@@ -11433,7 +11436,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>62</v>
       </c>
@@ -11471,7 +11474,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>62</v>
       </c>
@@ -11509,7 +11512,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>62</v>
       </c>
@@ -11547,7 +11550,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>62</v>
       </c>
@@ -11585,7 +11588,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>62</v>
       </c>
@@ -11623,7 +11626,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>62</v>
       </c>
@@ -11661,7 +11664,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -11699,7 +11702,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -11737,7 +11740,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>62</v>
       </c>
@@ -11775,7 +11778,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -11813,7 +11816,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>62</v>
       </c>
@@ -11851,7 +11854,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -11889,7 +11892,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -11927,7 +11930,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -11965,7 +11968,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>62</v>
       </c>
@@ -12003,7 +12006,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -12041,7 +12044,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -12079,7 +12082,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>62</v>
       </c>
@@ -12117,7 +12120,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>62</v>
       </c>
@@ -12155,7 +12158,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>62</v>
       </c>
@@ -12204,18 +12207,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L69"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.28515625" customWidth="1"/>
-    <col min="11" max="11" width="42.42578125" customWidth="1"/>
-    <col min="12" max="14" width="30.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" customWidth="1"/>
+    <col min="9" max="9" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="42.44140625" customWidth="1"/>
+    <col min="12" max="14" width="30.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -12253,7 +12256,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>664</v>
       </c>
@@ -12291,7 +12294,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>664</v>
       </c>
@@ -12329,7 +12332,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>664</v>
       </c>
@@ -12367,7 +12370,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>664</v>
       </c>
@@ -12405,7 +12408,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>664</v>
       </c>
@@ -12443,7 +12446,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>664</v>
       </c>
@@ -12481,7 +12484,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>664</v>
       </c>
@@ -12519,7 +12522,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>664</v>
       </c>
@@ -12557,7 +12560,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>664</v>
       </c>
@@ -12595,7 +12598,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>664</v>
       </c>
@@ -12633,7 +12636,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>664</v>
       </c>
@@ -12671,7 +12674,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>664</v>
       </c>
@@ -12709,7 +12712,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>664</v>
       </c>
@@ -12747,7 +12750,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>664</v>
       </c>
@@ -12785,7 +12788,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>664</v>
       </c>
@@ -12823,7 +12826,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>664</v>
       </c>
@@ -12861,7 +12864,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>664</v>
       </c>
@@ -12899,7 +12902,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>664</v>
       </c>
@@ -12937,7 +12940,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>664</v>
       </c>
@@ -12975,7 +12978,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>664</v>
       </c>
@@ -13013,7 +13016,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>664</v>
       </c>
@@ -13051,7 +13054,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>664</v>
       </c>
@@ -13089,7 +13092,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>665</v>
       </c>
@@ -13127,7 +13130,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>665</v>
       </c>
@@ -13165,7 +13168,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>665</v>
       </c>
@@ -13203,7 +13206,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>665</v>
       </c>
@@ -13241,7 +13244,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>665</v>
       </c>
@@ -13279,7 +13282,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>665</v>
       </c>
@@ -13317,7 +13320,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>665</v>
       </c>
@@ -13355,7 +13358,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>665</v>
       </c>
@@ -13393,7 +13396,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>665</v>
       </c>
@@ -13431,7 +13434,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>665</v>
       </c>
@@ -13469,7 +13472,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>665</v>
       </c>
@@ -13507,7 +13510,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>665</v>
       </c>
@@ -13545,7 +13548,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>665</v>
       </c>
@@ -13583,7 +13586,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>665</v>
       </c>
@@ -13621,7 +13624,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>665</v>
       </c>
@@ -13659,7 +13662,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>665</v>
       </c>
@@ -13697,7 +13700,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>665</v>
       </c>
@@ -13735,7 +13738,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>665</v>
       </c>
@@ -13773,7 +13776,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>665</v>
       </c>
@@ -13811,7 +13814,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>665</v>
       </c>
@@ -13849,7 +13852,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>665</v>
       </c>
@@ -13887,7 +13890,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>665</v>
       </c>
@@ -13925,7 +13928,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>663</v>
       </c>
@@ -13963,7 +13966,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>663</v>
       </c>
@@ -14001,7 +14004,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>663</v>
       </c>
@@ -14039,7 +14042,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>663</v>
       </c>
@@ -14077,7 +14080,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>663</v>
       </c>
@@ -14115,7 +14118,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>663</v>
       </c>
@@ -14153,7 +14156,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>663</v>
       </c>
@@ -14191,7 +14194,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>663</v>
       </c>
@@ -14229,7 +14232,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>663</v>
       </c>
@@ -14267,7 +14270,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>663</v>
       </c>
@@ -14305,7 +14308,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>663</v>
       </c>
@@ -14343,7 +14346,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>663</v>
       </c>
@@ -14381,7 +14384,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>663</v>
       </c>
@@ -14419,7 +14422,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>663</v>
       </c>
@@ -14457,7 +14460,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>663</v>
       </c>
@@ -14495,7 +14498,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>663</v>
       </c>
@@ -14533,7 +14536,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>663</v>
       </c>
@@ -14571,7 +14574,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>663</v>
       </c>
@@ -14609,7 +14612,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>663</v>
       </c>
@@ -14647,7 +14650,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>663</v>
       </c>
@@ -14685,7 +14688,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>663</v>
       </c>
@@ -14723,7 +14726,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>663</v>
       </c>
@@ -14761,7 +14764,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>663</v>
       </c>
@@ -14799,7 +14802,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>663</v>
       </c>
@@ -14848,16 +14851,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L67"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="32.42578125" customWidth="1"/>
-    <col min="8" max="8" width="41.5703125" customWidth="1"/>
-    <col min="10" max="10" width="60.140625" customWidth="1"/>
-    <col min="11" max="11" width="29.42578125" customWidth="1"/>
-    <col min="12" max="12" width="49.5703125" customWidth="1"/>
+    <col min="7" max="7" width="32.44140625" customWidth="1"/>
+    <col min="8" max="8" width="41.5546875" customWidth="1"/>
+    <col min="10" max="10" width="60.109375" customWidth="1"/>
+    <col min="11" max="11" width="29.44140625" customWidth="1"/>
+    <col min="12" max="12" width="49.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -14895,7 +14898,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1162</v>
       </c>
@@ -14933,7 +14936,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1162</v>
       </c>
@@ -14971,7 +14974,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1162</v>
       </c>
@@ -15009,7 +15012,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1162</v>
       </c>
@@ -15047,7 +15050,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1162</v>
       </c>
@@ -15085,7 +15088,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1162</v>
       </c>
@@ -15123,7 +15126,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1162</v>
       </c>
@@ -15161,7 +15164,7 @@
         <v>1651</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1162</v>
       </c>
@@ -15199,7 +15202,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1162</v>
       </c>
@@ -15237,7 +15240,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1162</v>
       </c>
@@ -15275,7 +15278,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1162</v>
       </c>
@@ -15313,7 +15316,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1162</v>
       </c>
@@ -15351,7 +15354,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1162</v>
       </c>
@@ -15389,7 +15392,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1162</v>
       </c>
@@ -15427,7 +15430,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1162</v>
       </c>
@@ -15465,7 +15468,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1162</v>
       </c>
@@ -15503,7 +15506,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1162</v>
       </c>
@@ -15541,7 +15544,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1162</v>
       </c>
@@ -15579,7 +15582,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1162</v>
       </c>
@@ -15617,7 +15620,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1162</v>
       </c>
@@ -15655,7 +15658,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1162</v>
       </c>
@@ -15693,7 +15696,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>1162</v>
       </c>
@@ -15731,7 +15734,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>1161</v>
       </c>
@@ -15769,7 +15772,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1161</v>
       </c>
@@ -15807,7 +15810,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>1161</v>
       </c>
@@ -15845,7 +15848,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>1161</v>
       </c>
@@ -15883,7 +15886,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>1161</v>
       </c>
@@ -15921,7 +15924,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>1161</v>
       </c>
@@ -15959,7 +15962,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>1161</v>
       </c>
@@ -15997,7 +16000,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1161</v>
       </c>
@@ -16035,7 +16038,7 @@
         <v>1653</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>1161</v>
       </c>
@@ -16073,7 +16076,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>1161</v>
       </c>
@@ -16111,7 +16114,7 @@
         <v>1658</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>1161</v>
       </c>
@@ -16149,7 +16152,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>1161</v>
       </c>
@@ -16187,7 +16190,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>1161</v>
       </c>
@@ -16225,7 +16228,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>1161</v>
       </c>
@@ -16263,7 +16266,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>1161</v>
       </c>
@@ -16301,7 +16304,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>1161</v>
       </c>
@@ -16339,7 +16342,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>1161</v>
       </c>
@@ -16377,7 +16380,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>1161</v>
       </c>
@@ -16415,7 +16418,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>1161</v>
       </c>
@@ -16453,7 +16456,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>1161</v>
       </c>
@@ -16491,7 +16494,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>1161</v>
       </c>
@@ -16529,7 +16532,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>1161</v>
       </c>
@@ -16567,7 +16570,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>1163</v>
       </c>
@@ -16605,7 +16608,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>1163</v>
       </c>
@@ -16643,7 +16646,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>1163</v>
       </c>
@@ -16681,7 +16684,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>1163</v>
       </c>
@@ -16719,7 +16722,7 @@
         <v>1643</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>1163</v>
       </c>
@@ -16757,7 +16760,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>1163</v>
       </c>
@@ -16795,7 +16798,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>1163</v>
       </c>
@@ -16833,7 +16836,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>1163</v>
       </c>
@@ -16871,7 +16874,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>1163</v>
       </c>
@@ -16909,7 +16912,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>1163</v>
       </c>
@@ -16947,7 +16950,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>1163</v>
       </c>
@@ -16985,7 +16988,7 @@
         <v>1663</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>1163</v>
       </c>
@@ -17023,7 +17026,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>1163</v>
       </c>
@@ -17061,7 +17064,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>1163</v>
       </c>
@@ -17099,7 +17102,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>1163</v>
       </c>
@@ -17137,7 +17140,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>1163</v>
       </c>
@@ -17175,7 +17178,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>1163</v>
       </c>
@@ -17213,7 +17216,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>1163</v>
       </c>
@@ -17251,7 +17254,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>1163</v>
       </c>
@@ -17289,7 +17292,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>1163</v>
       </c>
@@ -17327,7 +17330,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>1163</v>
       </c>
@@ -17365,7 +17368,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>1163</v>
       </c>
@@ -17414,13 +17417,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="32.85546875" customWidth="1"/>
+    <col min="7" max="7" width="32.88671875" customWidth="1"/>
     <col min="8" max="9" width="0" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
@@ -17455,7 +17459,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1697</v>
       </c>
@@ -17490,7 +17494,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1698</v>
       </c>
@@ -17525,7 +17529,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1699</v>
       </c>
@@ -17560,7 +17564,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1700</v>
       </c>
@@ -17595,7 +17599,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1701</v>
       </c>
@@ -17630,7 +17634,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1702</v>
       </c>
@@ -17665,7 +17669,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1703</v>
       </c>
@@ -17700,7 +17704,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1704</v>
       </c>
@@ -17735,7 +17739,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1705</v>
       </c>
@@ -17770,7 +17774,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1706</v>
       </c>
@@ -17805,7 +17809,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1707</v>
       </c>
@@ -17840,7 +17844,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1708</v>
       </c>
@@ -17875,7 +17879,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1709</v>
       </c>
@@ -17910,7 +17914,7 @@
         <v>2073</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1710</v>
       </c>
@@ -17945,7 +17949,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1711</v>
       </c>
@@ -17980,7 +17984,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1712</v>
       </c>
@@ -18015,7 +18019,7 @@
         <v>2076</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1713</v>
       </c>
@@ -18050,7 +18054,7 @@
         <v>2076</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1714</v>
       </c>
@@ -18085,7 +18089,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1715</v>
       </c>
@@ -18120,7 +18124,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1716</v>
       </c>
@@ -18155,7 +18159,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1717</v>
       </c>
@@ -18190,7 +18194,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>1718</v>
       </c>
@@ -18225,7 +18229,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>1719</v>
       </c>
@@ -18260,7 +18264,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1720</v>
       </c>
@@ -18295,7 +18299,7 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>1721</v>
       </c>
@@ -18330,7 +18334,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>1722</v>
       </c>
@@ -18365,7 +18369,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>1723</v>
       </c>
@@ -18400,7 +18404,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>1724</v>
       </c>
@@ -18435,7 +18439,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>1725</v>
       </c>
@@ -18470,7 +18474,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1726</v>
       </c>
@@ -18505,7 +18509,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>1727</v>
       </c>
@@ -18540,7 +18544,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>1728</v>
       </c>
@@ -18575,7 +18579,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>1729</v>
       </c>
@@ -18610,7 +18614,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>1730</v>
       </c>
@@ -18645,7 +18649,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>1731</v>
       </c>
@@ -18680,7 +18684,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>1732</v>
       </c>
@@ -18715,7 +18719,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>1733</v>
       </c>
@@ -18750,7 +18754,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>1734</v>
       </c>
@@ -18785,7 +18789,7 @@
         <v>2076</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>1735</v>
       </c>
@@ -18820,7 +18824,7 @@
         <v>2086</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>1736</v>
       </c>
@@ -18855,7 +18859,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>1737</v>
       </c>
@@ -18890,7 +18894,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>1738</v>
       </c>
@@ -18925,7 +18929,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>1739</v>
       </c>
@@ -18960,7 +18964,7 @@
         <v>2088</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>1740</v>
       </c>
@@ -18995,7 +18999,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>1741</v>
       </c>
@@ -19030,7 +19034,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>1742</v>
       </c>
@@ -19065,7 +19069,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>1743</v>
       </c>
@@ -19100,7 +19104,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>1744</v>
       </c>
@@ -19135,7 +19139,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>1745</v>
       </c>
@@ -19170,7 +19174,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>1746</v>
       </c>
@@ -19213,14 +19217,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K86"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="25.42578125" customWidth="1"/>
-    <col min="7" max="7" width="60.85546875" customWidth="1"/>
+    <col min="6" max="6" width="25.44140625" customWidth="1"/>
+    <col min="7" max="7" width="60.88671875" customWidth="1"/>
     <col min="8" max="9" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
@@ -19255,7 +19259,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2092</v>
       </c>
@@ -19290,7 +19294,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2094</v>
       </c>
@@ -19325,7 +19329,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2096</v>
       </c>
@@ -19360,7 +19364,7 @@
         <v>2755</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2097</v>
       </c>
@@ -19395,7 +19399,7 @@
         <v>2756</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2098</v>
       </c>
@@ -19430,7 +19434,7 @@
         <v>2757</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2099</v>
       </c>
@@ -19465,7 +19469,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2100</v>
       </c>
@@ -19500,7 +19504,7 @@
         <v>2759</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2101</v>
       </c>
@@ -19535,7 +19539,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2102</v>
       </c>
@@ -19570,7 +19574,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>2103</v>
       </c>
@@ -19605,7 +19609,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>2104</v>
       </c>
@@ -19640,7 +19644,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>2105</v>
       </c>
@@ -19675,7 +19679,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>2106</v>
       </c>
@@ -19710,7 +19714,7 @@
         <v>2765</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>2107</v>
       </c>
@@ -19745,7 +19749,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>2108</v>
       </c>
@@ -19780,7 +19784,7 @@
         <v>2767</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>2109</v>
       </c>
@@ -19815,7 +19819,7 @@
         <v>2768</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>2110</v>
       </c>
@@ -19850,7 +19854,7 @@
         <v>2769</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>2111</v>
       </c>
@@ -19885,7 +19889,7 @@
         <v>2770</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>2112</v>
       </c>
@@ -19920,7 +19924,7 @@
         <v>2771</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>2113</v>
       </c>
@@ -19955,7 +19959,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>2114</v>
       </c>
@@ -19990,7 +19994,7 @@
         <v>2773</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>2115</v>
       </c>
@@ -20025,7 +20029,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>2116</v>
       </c>
@@ -20060,7 +20064,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>2117</v>
       </c>
@@ -20095,7 +20099,7 @@
         <v>2775</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>2118</v>
       </c>
@@ -20130,7 +20134,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>2119</v>
       </c>
@@ -20165,7 +20169,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>2120</v>
       </c>
@@ -20200,7 +20204,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>2121</v>
       </c>
@@ -20235,7 +20239,7 @@
         <v>2777</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>2122</v>
       </c>
@@ -20270,7 +20274,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>2123</v>
       </c>
@@ -20305,7 +20309,7 @@
         <v>2779</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>2124</v>
       </c>
@@ -20340,7 +20344,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>2125</v>
       </c>
@@ -20375,7 +20379,7 @@
         <v>2780</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>2126</v>
       </c>
@@ -20410,7 +20414,7 @@
         <v>2781</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>2127</v>
       </c>
@@ -20445,7 +20449,7 @@
         <v>2782</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>2128</v>
       </c>
@@ -20480,7 +20484,7 @@
         <v>2783</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>2129</v>
       </c>
@@ -20515,7 +20519,7 @@
         <v>2784</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>2130</v>
       </c>
@@ -20550,7 +20554,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>2131</v>
       </c>
@@ -20585,7 +20589,7 @@
         <v>2785</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>2132</v>
       </c>
@@ -20620,7 +20624,7 @@
         <v>2786</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>2133</v>
       </c>
@@ -20655,7 +20659,7 @@
         <v>2787</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>2134</v>
       </c>
@@ -20690,7 +20694,7 @@
         <v>2788</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>2135</v>
       </c>
@@ -20725,7 +20729,7 @@
         <v>2789</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>2136</v>
       </c>
@@ -20760,7 +20764,7 @@
         <v>2790</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>2137</v>
       </c>
@@ -20795,7 +20799,7 @@
         <v>2791</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>2138</v>
       </c>
@@ -20830,7 +20834,7 @@
         <v>2792</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>2139</v>
       </c>
@@ -20865,7 +20869,7 @@
         <v>2755</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>2140</v>
       </c>
@@ -20900,7 +20904,7 @@
         <v>2793</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>2141</v>
       </c>
@@ -20935,7 +20939,7 @@
         <v>2794</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>2142</v>
       </c>
@@ -20970,7 +20974,7 @@
         <v>2795</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>2143</v>
       </c>
@@ -21005,7 +21009,7 @@
         <v>2777</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>2144</v>
       </c>
@@ -21040,7 +21044,7 @@
         <v>2796</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>2145</v>
       </c>
@@ -21075,7 +21079,7 @@
         <v>2797</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>2146</v>
       </c>
@@ -21110,7 +21114,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>2147</v>
       </c>
@@ -21145,7 +21149,7 @@
         <v>2799</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>2148</v>
       </c>
@@ -21180,7 +21184,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>2149</v>
       </c>
@@ -21215,7 +21219,7 @@
         <v>2801</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>2150</v>
       </c>
@@ -21250,7 +21254,7 @@
         <v>2802</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>2151</v>
       </c>
@@ -21285,7 +21289,7 @@
         <v>2782</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>2152</v>
       </c>
@@ -21320,7 +21324,7 @@
         <v>2803</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>2153</v>
       </c>
@@ -21355,7 +21359,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>2154</v>
       </c>
@@ -21390,7 +21394,7 @@
         <v>2805</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>2155</v>
       </c>
@@ -21425,7 +21429,7 @@
         <v>2806</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>2156</v>
       </c>
@@ -21460,7 +21464,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>2157</v>
       </c>
@@ -21495,7 +21499,7 @@
         <v>2799</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>2158</v>
       </c>
@@ -21530,7 +21534,7 @@
         <v>2808</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>2159</v>
       </c>
@@ -21565,7 +21569,7 @@
         <v>2799</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>2160</v>
       </c>
@@ -21600,7 +21604,7 @@
         <v>2809</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>2161</v>
       </c>
@@ -21635,7 +21639,7 @@
         <v>2810</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>2162</v>
       </c>
@@ -21670,7 +21674,7 @@
         <v>2811</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>2163</v>
       </c>
@@ -21705,7 +21709,7 @@
         <v>2812</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>2164</v>
       </c>
@@ -21740,7 +21744,7 @@
         <v>2813</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>2165</v>
       </c>
@@ -21775,7 +21779,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>2166</v>
       </c>
@@ -21810,7 +21814,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>2167</v>
       </c>
@@ -21845,7 +21849,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>2168</v>
       </c>
@@ -21880,7 +21884,7 @@
         <v>2815</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>2169</v>
       </c>
@@ -21915,7 +21919,7 @@
         <v>2816</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>2170</v>
       </c>
@@ -21950,7 +21954,7 @@
         <v>2817</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>2171</v>
       </c>
@@ -21985,7 +21989,7 @@
         <v>2818</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>2172</v>
       </c>
@@ -22020,7 +22024,7 @@
         <v>2819</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>2173</v>
       </c>
@@ -22055,7 +22059,7 @@
         <v>2799</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>2174</v>
       </c>
@@ -22090,7 +22094,7 @@
         <v>2820</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>2175</v>
       </c>
@@ -22125,7 +22129,7 @@
         <v>2821</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>2091</v>
       </c>
@@ -22160,7 +22164,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>2093</v>
       </c>
@@ -22195,7 +22199,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>2095</v>
       </c>
@@ -22241,28 +22245,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.140625" customWidth="1"/>
+    <col min="1" max="1" width="27.109375" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="9" max="9" width="25.85546875" customWidth="1"/>
+    <col min="9" max="9" width="25.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2842</v>
       </c>
@@ -22282,14 +22286,14 @@
         <v>2826</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>2843</v>
       </c>
@@ -22310,7 +22314,7 @@
       </c>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>2844</v>
       </c>
@@ -22331,7 +22335,7 @@
       </c>
       <c r="I6" s="7"/>
     </row>
-    <row r="7" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>2854</v>
       </c>
@@ -22352,7 +22356,7 @@
       </c>
       <c r="I7" s="7"/>
     </row>
-    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2855</v>
       </c>
@@ -22373,7 +22377,7 @@
       </c>
       <c r="I8" s="7"/>
     </row>
-    <row r="9" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>2856</v>
       </c>
@@ -22394,7 +22398,7 @@
       </c>
       <c r="I9" s="7"/>
     </row>
-    <row r="10" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>2859</v>
       </c>
@@ -22415,7 +22419,7 @@
       </c>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>2853</v>
       </c>
@@ -22436,7 +22440,7 @@
       </c>
       <c r="I11" s="7"/>
     </row>
-    <row r="12" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2845</v>
       </c>
@@ -22457,7 +22461,7 @@
       </c>
       <c r="I12" s="7"/>
     </row>
-    <row r="13" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>2849</v>
       </c>
@@ -22478,7 +22482,7 @@
       </c>
       <c r="I13" s="7"/>
     </row>
-    <row r="14" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>2857</v>
       </c>
@@ -22499,7 +22503,7 @@
       </c>
       <c r="I14" s="7"/>
     </row>
-    <row r="15" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>2858</v>
       </c>
@@ -22520,7 +22524,7 @@
       </c>
       <c r="I15" s="7"/>
     </row>
-    <row r="16" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>2852</v>
       </c>
@@ -22541,7 +22545,7 @@
       </c>
       <c r="I16" s="7"/>
     </row>
-    <row r="17" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>2847</v>
       </c>
@@ -22562,7 +22566,7 @@
       </c>
       <c r="I17" s="7"/>
     </row>
-    <row r="18" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>2846</v>
       </c>
@@ -22583,7 +22587,7 @@
       </c>
       <c r="I18" s="7"/>
     </row>
-    <row r="19" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>2850</v>
       </c>
@@ -22604,7 +22608,7 @@
       </c>
       <c r="I19" s="7"/>
     </row>
-    <row r="20" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -22612,7 +22616,7 @@
       <c r="F20" s="6"/>
       <c r="I20" s="7"/>
     </row>
-    <row r="21" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>2848</v>
       </c>
@@ -22633,64 +22637,64 @@
       </c>
       <c r="I21" s="7"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I22" s="7"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I23" s="7"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I24" s="7"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I25" s="7"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I26" s="7"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I27" s="7"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I28" s="7"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I29" s="7"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I30" s="7"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I32" s="7"/>
     </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I33" s="7"/>
     </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I34" s="7"/>
     </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I35" s="7"/>
     </row>
-    <row r="36" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I36" s="7"/>
     </row>
-    <row r="37" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I37" s="7"/>
     </row>
-    <row r="38" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I38" s="7"/>
     </row>
-    <row r="39" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I39" s="7"/>
     </row>
-    <row r="40" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I40" s="7"/>
     </row>
-    <row r="42" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I42" s="7"/>
     </row>
-    <row r="43" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I43" s="7"/>
     </row>
   </sheetData>
